--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487462_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487462_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4358</v>
+        <v>0.6939</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1968</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6325</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>1.0647</v>
@@ -610,13 +610,13 @@
         <v>0.1958</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8248</v>
+        <v>-0.5667</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2376</v>
+        <v>-0.0329</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5337</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0746</v>
+        <v>-0.3592</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1945</v>
+        <v>1.9634</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2691</v>
+        <v>-2.3226</v>
       </c>
       <c r="G3" t="n">
         <v>1.6816</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.148</v>
+        <v>-0.4326</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4734</v>
+        <v>0.2423</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6214</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2166</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.1708</v>
+        <v>-1.6704</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5208</v>
+        <v>0.8607</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6915</v>
+        <v>-2.5311</v>
       </c>
       <c r="G4" t="n">
         <v>2.1506</v>
@@ -766,13 +766,13 @@
         <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2223</v>
+        <v>-0.7219</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1323</v>
+        <v>-0.9719</v>
       </c>
       <c r="V4" t="n">
         <v>-3.0991</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.4383</v>
+        <v>-2.33</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8758</v>
+        <v>-1.7141</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5625</v>
+        <v>-0.616</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8006</v>
@@ -844,13 +844,13 @@
         <v>0.1958</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1249</v>
+        <v>0.2332</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0594</v>
+        <v>0.1023</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1843</v>
+        <v>0.1309</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.5465</v>
+        <v>-3.2614</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7015</v>
+        <v>-2.5233</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8451</v>
+        <v>-0.7382</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6185</v>
@@ -922,13 +922,13 @@
         <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0444</v>
+        <v>-0.7593</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5058</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3604</v>
+        <v>-0.2535</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8837</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>J. SEARA GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.581</v>
+        <v>-3.8551</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.3609</v>
+        <v>-3.2433</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7799</v>
+        <v>-0.6118</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8131</v>
+        <v>-2.0867</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7274</v>
+        <v>-2.0919</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0857</v>
+        <v>0.0052</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3088</v>
+        <v>-1.3441</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6975</v>
+        <v>-1.3441</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0063</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4957</v>
+        <v>-0.7427</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4249</v>
+        <v>-0.7479</v>
       </c>
       <c r="O7" t="n">
-        <v>1.9206</v>
+        <v>0.0052</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8962</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5407</v>
+        <v>-0.1232</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2358</v>
+        <v>-0.2541</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3049</v>
+        <v>0.1309</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6083</v>
+        <v>-0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6083</v>
+        <v>-0.6659</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SEARA GONZALEZ</t>
+          <t>J. RODRIGUEZ BARRIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1178</v>
+        <v>-4.2192</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3456</v>
+        <v>-2.4599</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7722</v>
+        <v>-1.7593</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0867</v>
+        <v>-3.2878</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0919</v>
+        <v>-1.6815</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0052</v>
+        <v>-1.6062</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3441</v>
+        <v>-1.9617</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3441</v>
+        <v>-0.5972</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.3645</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7427</v>
+        <v>-1.326</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7479</v>
+        <v>-1.0843</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0052</v>
+        <v>-0.2417</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3859</v>
+        <v>-0.5558</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3564</v>
+        <v>-0.4982</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0295</v>
+        <v>-0.0576</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6659</v>
+        <v>-1.159</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6758</v>
+        <v>-4.2353</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8309</v>
+        <v>-5.6944</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8449</v>
+        <v>1.4591</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.821</v>
+        <v>-0.8131</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0286</v>
+        <v>-0.7274</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7924</v>
+        <v>-0.0857</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1668</v>
+        <v>-1.3088</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6058</v>
+        <v>0.6975</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-2.0063</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6542</v>
+        <v>0.4957</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4228</v>
+        <v>-1.4249</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2314</v>
+        <v>1.9206</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5668</v>
+        <v>-3.917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9377</v>
+        <v>-4.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5634</v>
+        <v>-0.1135</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0018</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5617</v>
+        <v>-0.0159</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BARRIO</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8021</v>
+        <v>-5.0093</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1497</v>
+        <v>-4.1644</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6524</v>
+        <v>-0.8449</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2878</v>
+        <v>-2.821</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6815</v>
+        <v>-2.0286</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6062</v>
+        <v>-0.7924</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9617</v>
+        <v>-1.1668</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5972</v>
+        <v>-0.6058</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3645</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.326</v>
+        <v>-1.6542</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0843</v>
+        <v>-1.4228</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2417</v>
+        <v>-0.2314</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7834</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1387</v>
+        <v>-0.8969</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.188</v>
+        <v>-0.3352</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0493</v>
+        <v>-0.5617</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.159</v>
+        <v>0.2754</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8624</v>
+        <v>-5.1026</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5274</v>
+        <v>-4.821</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3351</v>
+        <v>-0.2816</v>
       </c>
       <c r="G11" t="n">
         <v>1.2389</v>
@@ -1312,13 +1312,13 @@
         <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9517</v>
+        <v>-1.1919</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1592</v>
+        <v>-0.4529</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7924</v>
+        <v>-0.739</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0576</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.8335</v>
+        <v>-29.3486</v>
       </c>
       <c r="E12" t="n">
-        <v>-23.2733</v>
+        <v>-21.7884</v>
       </c>
       <c r="F12" t="n">
         <v>-7.5604</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.2919</v>
+        <v>-5.291900000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-3.400599999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8911</v>
+        <v>-1.891099999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1.234599999999999</v>
+        <v>1.2346</v>
       </c>
       <c r="K12" t="n">
-        <v>6.088100000000001</v>
+        <v>6.0881</v>
       </c>
       <c r="L12" t="n">
         <v>-4.8536</v>
@@ -1375,7 +1375,7 @@
         <v>-6.5265</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.488999999999999</v>
+        <v>-9.489000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>2.962400000000001</v>
@@ -1390,10 +1390,10 @@
         <v>8.812899999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.6136</v>
+        <v>-5.1286</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0672</v>
+        <v>-1.5821</v>
       </c>
       <c r="U12" t="n">
         <v>-3.5464</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3396</v>
+        <v>6.4896</v>
       </c>
       <c r="E13" t="n">
-        <v>6.3429</v>
+        <v>5.6266</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9967</v>
+        <v>0.8631</v>
       </c>
       <c r="G13" t="n">
         <v>1.7465</v>
@@ -1468,13 +1468,13 @@
         <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3765</v>
+        <v>0.5265</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0851</v>
+        <v>0.3688</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2914</v>
+        <v>0.1578</v>
       </c>
       <c r="V13" t="n">
         <v>3.0415</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1912</v>
+        <v>6.0225</v>
       </c>
       <c r="E14" t="n">
-        <v>2.735</v>
+        <v>2.3257</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4562</v>
+        <v>3.6968</v>
       </c>
       <c r="G14" t="n">
         <v>2.322</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3819</v>
+        <v>1.2132</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0963</v>
+        <v>0.6869</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2857</v>
+        <v>0.5262</v>
       </c>
       <c r="V14" t="n">
         <v>0.3329</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7034</v>
+        <v>5.5275</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3977</v>
+        <v>1.4025</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3057</v>
+        <v>4.125</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8524</v>
+        <v>2.2821</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9436</v>
+        <v>1.5999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0912</v>
+        <v>0.6822</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7107</v>
+        <v>2.1301</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3477</v>
+        <v>2.004</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.637</v>
+        <v>0.1261</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1416</v>
+        <v>0.152</v>
       </c>
       <c r="N15" t="n">
         <v>-0.4041</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5458</v>
+        <v>0.5562</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1751</v>
+        <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4593</v>
+        <v>0.5623</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4703</v>
+        <v>-0.1988</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.011</v>
+        <v>0.7611</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2166</v>
+        <v>0.3329</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4343</v>
+        <v>5.4231</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0955</v>
+        <v>4.0907</v>
       </c>
       <c r="F16" t="n">
-        <v>4.3389</v>
+        <v>1.3325</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2821</v>
+        <v>1.8524</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5999</v>
+        <v>1.9436</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6822</v>
+        <v>-0.0912</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1301</v>
+        <v>1.7107</v>
       </c>
       <c r="K16" t="n">
-        <v>2.004</v>
+        <v>2.3477</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1261</v>
+        <v>-0.637</v>
       </c>
       <c r="M16" t="n">
-        <v>0.152</v>
+        <v>0.1416</v>
       </c>
       <c r="N16" t="n">
         <v>-0.4041</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5562</v>
+        <v>0.5458</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.546</v>
+        <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4691</v>
+        <v>1.1791</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5058</v>
+        <v>1.1633</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9749</v>
+        <v>0.0157</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3329</v>
+        <v>1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3329</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.8465</v>
+        <v>4.8198</v>
       </c>
       <c r="E17" t="n">
         <v>1.9585</v>
       </c>
       <c r="F17" t="n">
-        <v>2.888</v>
+        <v>2.8613</v>
       </c>
       <c r="G17" t="n">
         <v>2.7518</v>
@@ -1780,13 +1780,13 @@
         <v>2.9377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3321</v>
+        <v>0.3054</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4815</v>
+        <v>0.4548</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7214</v>
+        <v>4.6283</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8456</v>
+        <v>3.5386</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8758</v>
+        <v>1.0896</v>
       </c>
       <c r="G18" t="n">
         <v>2.3186</v>
@@ -1858,13 +1858,13 @@
         <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6401</v>
+        <v>0.547</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8475</v>
+        <v>0.5405</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2074</v>
+        <v>0.0065</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.3009</v>
+        <v>3.8557</v>
       </c>
       <c r="E19" t="n">
-        <v>1.263</v>
+        <v>1.0584</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0379</v>
+        <v>2.7973</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0083</v>
@@ -1936,13 +1936,13 @@
         <v>1.7626</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9971</v>
+        <v>0.5518</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6099</v>
+        <v>0.4052</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3872</v>
+        <v>0.1466</v>
       </c>
       <c r="V19" t="n">
         <v>1.5495</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1707</v>
+        <v>1.4243</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3329</v>
+        <v>-1.0259</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5036</v>
+        <v>2.4502</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4551</v>
@@ -2014,13 +2014,13 @@
         <v>2.7419</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1368</v>
+        <v>0.1167</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4288</v>
+        <v>-0.1218</v>
       </c>
       <c r="U20" t="n">
-        <v>0.292</v>
+        <v>0.2385</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.408</v>
+        <v>0.9907</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8398</v>
+        <v>-0.1235</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2478</v>
+        <v>1.1142</v>
       </c>
       <c r="G21" t="n">
         <v>-0.328</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0473</v>
+        <v>0.5353</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5764</v>
+        <v>0.14</v>
       </c>
       <c r="U21" t="n">
-        <v>0.529</v>
+        <v>0.3954</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8387</v>
+        <v>-0.6653</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3642</v>
+        <v>-1.0572</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5255</v>
+        <v>0.3919</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3232</v>
@@ -2170,13 +2170,13 @@
         <v>0.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2608</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3388</v>
+        <v>-0.0318</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0779</v>
+        <v>-0.0557</v>
       </c>
       <c r="V22" t="n">
         <v>0.9412</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8866</v>
+        <v>-2.6949</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.49</v>
+        <v>-3.5924</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6034</v>
+        <v>0.8975</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8531</v>
@@ -2248,13 +2248,13 @@
         <v>1.7626</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3789</v>
+        <v>0.5706</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3305</v>
+        <v>0.2282</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0484</v>
+        <v>0.3424</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2166</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5572</v>
+        <v>-4.9875</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.0509</v>
+        <v>-6.6416</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4937</v>
+        <v>1.6541</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0138</v>
@@ -2326,13 +2326,13 @@
         <v>1.5668</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0234</v>
+        <v>0.5931</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1059</v>
+        <v>0.5152</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0825</v>
+        <v>0.0779</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>30.83349999999999</v>
+        <v>30.83379999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>7.560399999999998</v>
+        <v>7.560399999999996</v>
       </c>
       <c r="F25" t="n">
-        <v>23.2732</v>
+        <v>23.2735</v>
       </c>
       <c r="G25" t="n">
         <v>5.2919</v>
@@ -2404,13 +2404,13 @@
         <v>21.5433</v>
       </c>
       <c r="S25" t="n">
-        <v>6.613499999999999</v>
+        <v>6.6135</v>
       </c>
       <c r="T25" t="n">
         <v>3.5463</v>
       </c>
       <c r="U25" t="n">
-        <v>3.0671</v>
+        <v>3.0672</v>
       </c>
       <c r="V25" t="n">
         <v>6.198</v>
